--- a/data/trans_camb/IP16A98-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 39,87</t>
+          <t>0,65; 40,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 61,01</t>
+          <t>4,22; 62,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 6,77</t>
+          <t>-33,05; 7,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 16,4</t>
+          <t>-27,47; 14,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 15,4</t>
+          <t>-12,62; 15,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 36,77</t>
+          <t>-4,58; 38,7</t>
         </is>
       </c>
     </row>
@@ -717,29 +717,29 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 125,65</t>
+          <t>-100,0; 163,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,32; 192,25</t>
+          <t>-75,57; 189,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 268,23</t>
+          <t>-64,12; 241,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 758,02</t>
+          <t>-35,57; 832,16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 15,36</t>
+          <t>-15,34; 13,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 16,17</t>
+          <t>-22,56; 15,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 13,35</t>
+          <t>-15,26; 14,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 9,29</t>
+          <t>-14,8; 10,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 9,66</t>
+          <t>-10,12; 10,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 9,49</t>
+          <t>-11,4; 8,93</t>
         </is>
       </c>
     </row>
@@ -863,39 +863,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,36; 640,91</t>
+          <t>-84,15; 452,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,06; 286,4</t>
+          <t>-81,75; 269,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 494,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,33; 281,2</t>
+          <t>-75,19; 332,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 153,29</t>
+          <t>-68,8; 214,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 148,56</t>
+          <t>-62,85; 140,9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 39,0</t>
+          <t>-19,23; 34,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 21,62</t>
+          <t>-24,22; 20,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 41,9</t>
+          <t>-13,2; 39,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 37,27</t>
+          <t>-2,2; 37,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 29,38</t>
+          <t>-7,91; 27,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 23,8</t>
+          <t>-4,62; 25,19</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,64; 809,34</t>
+          <t>-100,0; 546,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,25; 447,76</t>
+          <t>-81,25; 388,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 1048,56</t>
+          <t>-34,13; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 335,76</t>
+          <t>-46,29; 428,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 351,51</t>
+          <t>-26,78; 368,71</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 38,49</t>
+          <t>3,2; 38,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 41,48</t>
+          <t>-1,8; 44,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 36,98</t>
+          <t>-13,22; 34,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 30,39</t>
+          <t>-24,85; 34,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 31,54</t>
+          <t>2,62; 31,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 28,93</t>
+          <t>-6,37; 28,16</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,66; —</t>
+          <t>-18,47; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,71; —</t>
+          <t>-69,27; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 684,45</t>
+          <t>-45,76; 583,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 830,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 561,81</t>
+          <t>4,39; 574,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 535,68</t>
+          <t>-49,59; 431,43</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 45,36</t>
+          <t>-9,47; 46,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 41,62</t>
+          <t>-3,6; 40,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 59,88</t>
+          <t>-6,23; 58,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 56,11</t>
+          <t>-2,92; 56,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 36,23</t>
+          <t>-4,59; 37,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 41,45</t>
+          <t>1,75; 39,84</t>
         </is>
       </c>
     </row>
@@ -1356,14 +1356,14 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,72; —</t>
+          <t>-57,53; —</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 15,0</t>
+          <t>-40,42; 15,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 5,75</t>
+          <t>-47,54; 6,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 66,08</t>
+          <t>0,4; 65,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 33,05</t>
+          <t>-8,37; 31,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 31,76</t>
+          <t>-9,05; 34,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 13,75</t>
+          <t>-18,42; 13,69</t>
         </is>
       </c>
     </row>
@@ -1497,29 +1497,29 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 1839,37</t>
+          <t>-37,98; 1711,2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-68,04; —</t>
+          <t>-63,62; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 347,05</t>
+          <t>-42,01; 358,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 183,08</t>
+          <t>-74,57; 158,61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 25,55</t>
+          <t>-7,04; 23,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 22,77</t>
+          <t>-4,85; 22,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 10,74</t>
+          <t>-23,62; 13,7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 28,95</t>
+          <t>-10,87; 31,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 12,17</t>
+          <t>-12,93; 11,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 24,35</t>
+          <t>-2,66; 24,05</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>-56,45; 746,3</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-52,16; 1054,79</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-58,55; 440,15</t>
+          <t>-60,78; 529,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-77,07; 219,02</t>
+          <t>-83,3; 171,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 384,73</t>
+          <t>-29,56; 356,21</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 6,07</t>
+          <t>-28,54; 6,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 53,16</t>
+          <t>-9,21; 50,27</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 18,95</t>
+          <t>-24,46; 17,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 24,34</t>
+          <t>-28,14; 23,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 8,34</t>
+          <t>-20,4; 7,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 28,03</t>
+          <t>-14,18; 25,15</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-87,74; 84,4</t>
+          <t>-86,69; 81,56</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 424,49</t>
+          <t>-39,56; 412,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-61,08; 141,89</t>
+          <t>-64,06; 133,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 205,13</t>
+          <t>-82,25; 211,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 54,65</t>
+          <t>-63,29; 48,36</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 178,25</t>
+          <t>-54,16; 151,36</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 11,83</t>
+          <t>-0,93; 12,88</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 15,75</t>
+          <t>-2,44; 16,88</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 13,49</t>
+          <t>-2,54; 12,61</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 11,53</t>
+          <t>-4,58; 10,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,12</t>
+          <t>-0,1; 10,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,9</t>
+          <t>-1,95; 10,57</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 132,68</t>
+          <t>-7,41; 143,36</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 167,95</t>
+          <t>-18,97; 175,55</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 121,69</t>
+          <t>-14,46; 109,24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 99,37</t>
+          <t>-24,46; 87,97</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,52; 87,15</t>
+          <t>-0,24; 89,39</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 92,75</t>
+          <t>-10,18; 87,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 40,46</t>
+          <t>1,98; 40,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 62,29</t>
+          <t>3,98; 65,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 7,37</t>
+          <t>-32,53; 6,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 14,81</t>
+          <t>-24,32; 16,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 15,44</t>
+          <t>-10,76; 15,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 38,7</t>
+          <t>-5,12; 37,91</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 163,96</t>
+          <t>-100,0; 115,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 189,12</t>
+          <t>-75,35; 158,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 241,34</t>
+          <t>-57,62; 257,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 832,16</t>
+          <t>-38,48; 739,65</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 13,65</t>
+          <t>-15,72; 14,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 15,08</t>
+          <t>-22,4; 13,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 14,43</t>
+          <t>-13,37; 13,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 10,47</t>
+          <t>-15,21; 10,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 10,16</t>
+          <t>-10,55; 9,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 8,93</t>
+          <t>-11,5; 8,84</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,15; 452,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,75; 269,42</t>
+          <t>-83,27; 228,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,7; 524,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 332,0</t>
+          <t>-79,06; 294,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 214,04</t>
+          <t>-68,09; 180,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 140,9</t>
+          <t>-63,89; 144,14</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 34,99</t>
+          <t>-18,53; 34,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 20,37</t>
+          <t>-19,74; 21,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 39,42</t>
+          <t>-10,64; 37,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 37,78</t>
+          <t>-3,53; 36,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 27,94</t>
+          <t>-8,0; 27,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 25,19</t>
+          <t>-5,65; 24,16</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 546,87</t>
+          <t>-100,0; 630,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 388,65</t>
+          <t>-75,08; 410,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,13; —</t>
+          <t>-43,22; 1003,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 428,93</t>
+          <t>-51,36; 423,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 368,71</t>
+          <t>-36,73; 342,46</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 38,02</t>
+          <t>3,76; 39,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 44,21</t>
+          <t>-1,3; 44,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 34,38</t>
+          <t>-9,05; 35,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 34,5</t>
+          <t>-23,6; 32,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 31,41</t>
+          <t>2,29; 29,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 28,16</t>
+          <t>-6,55; 27,15</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,47; —</t>
+          <t>-14,96; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,27; —</t>
+          <t>-72,46; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 583,75</t>
+          <t>-38,2; 618,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 830,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 574,27</t>
+          <t>7,46; 577,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 431,43</t>
+          <t>-46,76; 438,35</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 46,57</t>
+          <t>-9,51; 42,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 40,16</t>
+          <t>-1,77; 45,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 58,58</t>
+          <t>-6,36; 58,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 56,13</t>
+          <t>-4,01; 53,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 37,96</t>
+          <t>-3,12; 36,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 39,84</t>
+          <t>1,94; 41,04</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,53; —</t>
+          <t>-70,43; —</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 15,78</t>
+          <t>-42,3; 15,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 6,16</t>
+          <t>-51,43; 2,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,4; 65,09</t>
+          <t>-3,47; 63,43</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 31,62</t>
+          <t>-11,01; 31,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 34,68</t>
+          <t>-7,95; 33,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 13,69</t>
+          <t>-18,33; 15,74</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 330,51</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-37,78; 1444,99</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-68,8; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-35,46; 387,16</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-37,98; 1711,2</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-63,62; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-42,01; 358,92</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-74,57; 158,61</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 23,78</t>
+          <t>-8,13; 23,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 22,13</t>
+          <t>-5,03; 22,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 13,7</t>
+          <t>-22,07; 15,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 31,11</t>
+          <t>-9,62; 30,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 11,92</t>
+          <t>-11,86; 12,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 24,05</t>
+          <t>-4,02; 23,08</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 746,3</t>
+          <t>-56,71; 897,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 529,69</t>
+          <t>-50,95; 370,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 171,6</t>
+          <t>-81,08; 207,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 356,21</t>
+          <t>-31,99; 342,8</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 6,14</t>
+          <t>-28,98; 7,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 50,27</t>
+          <t>-9,95; 50,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 17,16</t>
+          <t>-24,33; 17,75</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 23,89</t>
+          <t>-29,3; 23,72</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 7,74</t>
+          <t>-17,66; 8,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 25,15</t>
+          <t>-13,89; 27,46</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-86,69; 81,56</t>
+          <t>-88,21; 78,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 412,55</t>
+          <t>-46,68; 472,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 133,04</t>
+          <t>-67,49; 122,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 211,27</t>
+          <t>-84,24; 184,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,29; 48,36</t>
+          <t>-59,26; 58,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 151,36</t>
+          <t>-48,77; 184,04</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,88</t>
+          <t>-1,63; 12,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 16,88</t>
+          <t>-2,55; 15,77</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 12,61</t>
+          <t>-2,05; 13,37</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,36</t>
+          <t>-3,81; 11,73</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 10,03</t>
+          <t>-0,4; 10,16</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 10,57</t>
+          <t>-1,22; 10,97</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 143,36</t>
+          <t>-11,62; 132,4</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 175,55</t>
+          <t>-19,55; 155,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 109,24</t>
+          <t>-12,69; 108,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 87,97</t>
+          <t>-20,72; 102,43</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 89,39</t>
+          <t>-3,15; 86,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 87,63</t>
+          <t>-7,33; 97,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Provincia-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-11,06</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>17,61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-11,06</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>4,38</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 40,53</t>
+          <t>-35,1; 6,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 65,07</t>
+          <t>-24,3; 17,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 6,09</t>
+          <t>0,66; 39,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 16,21</t>
+          <t>-0,52; 27,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 15,65</t>
+          <t>-12,16; 15,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 37,91</t>
+          <t>-9,28; 16,49</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-51,52%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-13,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>462,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>650,76%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-51,52%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-17,4%</t>
+          <t>340,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 125,65</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-71,79; 195,64</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 115,37</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-75,35; 158,48</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,62; 257,79</t>
+          <t>-60,58; 268,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 739,65</t>
+          <t>-47,06; 283,9</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,52</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 14,44</t>
+          <t>-15,18; 13,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 13,3</t>
+          <t>-15,81; 8,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 13,37</t>
+          <t>-15,6; 15,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 10,15</t>
+          <t>-9,56; 23,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 9,7</t>
+          <t>-11,48; 9,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 8,84</t>
+          <t>-7,23; 11,74</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-11,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-14,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-3,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-11,75%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,14%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,03%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 494,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 228,02</t>
+          <t>-81,97; 279,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,7; 524,44</t>
+          <t>-86,36; 640,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,06; 294,79</t>
+          <t>-52,07; 610,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 180,8</t>
+          <t>-73,17; 153,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,89; 144,14</t>
+          <t>-47,3; 209,34</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>6,13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,53</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,83</t>
+          <t>-1,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 34,6</t>
+          <t>-13,31; 41,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 21,06</t>
+          <t>-4,63; 32,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 37,59</t>
+          <t>-17,79; 39,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 36,95</t>
+          <t>-21,51; 19,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 27,57</t>
+          <t>-9,15; 29,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 24,16</t>
+          <t>-6,95; 20,3</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>35,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76,15%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170,26%</t>
+          <t>-6,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 630,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,08; 410,64</t>
+          <t>-47,79; 928,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,64; 809,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 1003,7</t>
+          <t>-79,62; 368,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 423,56</t>
+          <t>-67,22; 335,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 342,46</t>
+          <t>-38,06; 306,33</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,89</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17,88</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13,41</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>19,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>9,99</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 39,56</t>
+          <t>-7,67; 36,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 44,2</t>
+          <t>-23,55; 31,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 35,61</t>
+          <t>2,73; 38,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 32,78</t>
+          <t>0,72; 44,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 29,99</t>
+          <t>4,86; 31,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 27,15</t>
+          <t>-6,65; 30,97</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>73,69%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-10,4%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>310,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>261,46%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-10,22%</t>
+          <t>290,77%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,96; —</t>
+          <t>-31,93; 684,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,46; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 618,67</t>
+          <t>-6,66; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,0; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 577,86</t>
+          <t>10,16; 561,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 438,35</t>
+          <t>-50,66; 550,38</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17,99</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>23,91</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>7,07</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>14,63</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17,99</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20,75</t>
+          <t>15,91</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,19</t>
+          <t>20,28</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 42,33</t>
+          <t>-6,2; 59,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 45,51</t>
+          <t>0,01; 61,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 58,29</t>
+          <t>-9,54; 45,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 53,32</t>
+          <t>-2,07; 43,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 36,4</t>
+          <t>-2,81; 36,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 41,04</t>
+          <t>2,4; 43,99</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>311,34%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>413,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>147,92%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>306,3%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>311,34%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>359,09%</t>
+          <t>333,03%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>347,61%</t>
+          <t>387,39%</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-70,43; —</t>
+          <t>-47,66; —</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>32,06</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7,86</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-13,62</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-20,7</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>32,06</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>-19,75</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 15,53</t>
+          <t>1,61; 66,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 2,38</t>
+          <t>-12,35; 32,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 63,43</t>
+          <t>-42,13; 15,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 31,94</t>
+          <t>-46,39; 8,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 33,97</t>
+          <t>-10,84; 31,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 15,74</t>
+          <t>-19,24; 13,74</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>268,17%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>65,75%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-49,82%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-75,71%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>268,17%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>-72,22%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-14,21%</t>
+          <t>-16,07%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 330,51</t>
+          <t>-13,76; 1839,37</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-72,17; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-37,78; 1444,99</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-68,8; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 387,16</t>
+          <t>-47,62; 347,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,7; 179,65</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-8,68</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>5,23</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-8,68</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>8,01</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 23,97</t>
+          <t>-22,68; 10,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 22,98</t>
+          <t>-10,91; 33,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 15,23</t>
+          <t>-8,25; 25,55</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 30,02</t>
+          <t>-4,73; 23,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 12,48</t>
+          <t>-11,7; 12,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 23,08</t>
+          <t>-2,88; 24,5</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-56,34%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>42,81%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>67,56%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>104,99%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-56,34%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>106,73%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -1648,27 +1648,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 897,71</t>
+          <t>-59,03; 587,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 370,31</t>
+          <t>-53,7; 1083,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-81,08; 207,51</t>
+          <t>-77,07; 219,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 342,8</t>
+          <t>-28,9; 391,15</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-2,78</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-4,38</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-10,58</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>19,98</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-5,04</t>
+          <t>24,36</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>7,36</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 7,39</t>
+          <t>-23,61; 18,95</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 50,67</t>
+          <t>-31,08; 25,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 17,75</t>
+          <t>-27,57; 6,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 23,72</t>
+          <t>-7,95; 57,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 8,8</t>
+          <t>-19,38; 8,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 27,46</t>
+          <t>-12,92; 30,67</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-10,69%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-16,84%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-47,93%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-10,69%</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-19,4%</t>
+          <t>110,38%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-88,21; 78,96</t>
+          <t>-61,08; 141,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 472,51</t>
+          <t>-100,0; 216,75</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 122,8</t>
+          <t>-87,74; 84,4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-84,24; 184,78</t>
+          <t>-36,87; 471,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 58,63</t>
+          <t>-63,58; 54,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-48,77; 184,04</t>
+          <t>-47,15; 191,36</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5,13</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>4,92</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>5,18</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 12,02</t>
+          <t>-2,63; 13,49</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 15,77</t>
+          <t>-4,24; 12,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 13,37</t>
+          <t>-1,99; 11,83</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,73</t>
+          <t>0,18; 14,64</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 10,16</t>
+          <t>-0,06; 10,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,97</t>
+          <t>0,35; 10,25</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>40,69%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 132,4</t>
+          <t>-14,01; 121,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 155,84</t>
+          <t>-25,18; 102,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 108,96</t>
+          <t>-13,87; 132,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 102,43</t>
+          <t>-0,41; 162,65</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 86,3</t>
+          <t>1,52; 87,15</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 97,83</t>
+          <t>2,87; 89,77</t>
         </is>
       </c>
     </row>
